--- a/metadata/gongfa/catalog.xlsx
+++ b/metadata/gongfa/catalog.xlsx
@@ -485,7 +485,7 @@
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>合计410条；原登记库 79；此前四HTML 211；Solve已审首24 24；HTML续提 96；输入：31c4f0e89cc2c0c1fd68caeb79af18da66ebb1a0f624dafca9e7efd62870a7a7</t>
+          <t>合计410条；原登记库 79；此前四HTML 211；Solve已审首24 24；HTML续提 96；输入：f78e799ed13956b958831310efb201cfd7b2339d6863e40b02139211bba7faf2</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
   "source": {
     "id": "repo-thinking-models-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/thinking-models.md",
+    "path": "docs/gongfa/thinking-models.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-thinking-models-81fc7ae.txt",
@@ -804,7 +804,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -941,7 +941,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -1081,7 +1081,7 @@
   "source": {
     "id": "repo-glue-coding-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/concepts/glue-coding.md",
+    "path": "docs/gongfa/glue-coding.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-glue-coding-81fc7ae.txt",
@@ -1196,7 +1196,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -1338,7 +1338,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -1477,7 +1477,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -1619,7 +1619,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -2202,7 +2202,7 @@
   "source": {
     "id": "repo-problem-solving-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/concepts/problem-solving.md",
+    "path": "docs/gongfa/problem-solving.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.365887Z",
     "snapshot_path": "metadata/gongfa/source-problem-solving-81fc7ae.txt",
@@ -2679,7 +2679,7 @@
   "source": {
     "id": "repo-thinking-models-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/thinking-models.md",
+    "path": "docs/gongfa/thinking-models.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-thinking-models-81fc7ae.txt",
@@ -2814,7 +2814,7 @@
   "source": {
     "id": "repo-thinking-models-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/thinking-models.md",
+    "path": "docs/gongfa/thinking-models.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-thinking-models-81fc7ae.txt",
@@ -2935,7 +2935,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -3076,7 +3076,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -3215,7 +3215,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -3358,7 +3358,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -3638,7 +3638,7 @@
   "source": {
     "id": "repo-system-building-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/concepts/system-building.md",
+    "path": "docs/gongfa/system-building.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.363591Z",
     "snapshot_path": "metadata/gongfa/source-system-building-81fc7ae.txt",
@@ -3749,7 +3749,7 @@
   "source": {
     "id": "repo-programming-dao-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/programming-dao.md",
+    "path": "docs/gongfa/programming-dao.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.370173Z",
     "snapshot_path": "metadata/gongfa/source-programming-dao-81fc7ae.txt",
@@ -3869,7 +3869,7 @@
   "source": {
     "id": "repo-software-engineering-truths-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/software-engineering-truths.md",
+    "path": "docs/gongfa/software-engineering-truths.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.243253Z",
     "snapshot_path": "metadata/gongfa/source-software-engineering-truths-81fc7ae.txt",
@@ -4014,7 +4014,7 @@
   "source": {
     "id": "repo-dataset-first-data-service-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/references/dataset-first-data-service.md",
+    "path": "docs/gongfa/dataset-first-data-service.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.245521Z",
     "snapshot_path": "metadata/gongfa/source-dataset-first-data-service-81fc7ae.txt",
@@ -4127,7 +4127,7 @@
   "source": {
     "id": "repo-dataset-first-data-service-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/references/dataset-first-data-service.md",
+    "path": "docs/gongfa/dataset-first-data-service.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.245521Z",
     "snapshot_path": "metadata/gongfa/source-dataset-first-data-service-81fc7ae.txt",
@@ -4259,7 +4259,7 @@
   "source": {
     "id": "repo-quality-gates-and-pitfalls-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/references/quality-gates-and-pitfalls.md",
+    "path": "docs/gongfa/quality-gates-and-pitfalls.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.250898Z",
     "snapshot_path": "metadata/gongfa/source-quality-gates-and-pitfalls-81fc7ae.txt",
@@ -10659,7 +10659,7 @@
   "source": {
     "id": "repo-thinking-models-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/thinking-models.md",
+    "path": "docs/gongfa/thinking-models.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-thinking-models-81fc7ae.txt",
@@ -10783,7 +10783,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -10925,7 +10925,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -11067,7 +11067,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -11206,7 +11206,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -11344,7 +11344,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -11752,7 +11752,7 @@
   "source": {
     "id": "repo-system-building-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/concepts/system-building.md",
+    "path": "docs/gongfa/system-building.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.363591Z",
     "snapshot_path": "metadata/gongfa/source-system-building-81fc7ae.txt",
@@ -11866,7 +11866,7 @@
   "source": {
     "id": "repo-programming-dao-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/programming-dao.md",
+    "path": "docs/gongfa/programming-dao.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.370173Z",
     "snapshot_path": "metadata/gongfa/source-programming-dao-81fc7ae.txt",
@@ -11983,7 +11983,7 @@
   "source": {
     "id": "repo-programming-dao-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/programming-dao.md",
+    "path": "docs/gongfa/programming-dao.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.370173Z",
     "snapshot_path": "metadata/gongfa/source-programming-dao-81fc7ae.txt",
@@ -12100,7 +12100,7 @@
   "source": {
     "id": "repo-programming-dao-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/programming-dao.md",
+    "path": "docs/gongfa/programming-dao.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.370173Z",
     "snapshot_path": "metadata/gongfa/source-programming-dao-81fc7ae.txt",
@@ -12217,7 +12217,7 @@
   "source": {
     "id": "repo-programming-dao-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/programming-dao.md",
+    "path": "docs/gongfa/programming-dao.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.370173Z",
     "snapshot_path": "metadata/gongfa/source-programming-dao-81fc7ae.txt",
@@ -12337,7 +12337,7 @@
   "source": {
     "id": "repo-programming-dao-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/programming-dao.md",
+    "path": "docs/gongfa/programming-dao.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.370173Z",
     "snapshot_path": "metadata/gongfa/source-programming-dao-81fc7ae.txt",
@@ -12453,7 +12453,7 @@
   "source": {
     "id": "repo-programming-dao-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/programming-dao.md",
+    "path": "docs/gongfa/programming-dao.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.370173Z",
     "snapshot_path": "metadata/gongfa/source-programming-dao-81fc7ae.txt",
@@ -12573,7 +12573,7 @@
   "source": {
     "id": "repo-software-engineering-truths-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/software-engineering-truths.md",
+    "path": "docs/gongfa/software-engineering-truths.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.243253Z",
     "snapshot_path": "metadata/gongfa/source-software-engineering-truths-81fc7ae.txt",
@@ -12692,7 +12692,7 @@
   "source": {
     "id": "repo-software-engineering-truths-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/software-engineering-truths.md",
+    "path": "docs/gongfa/software-engineering-truths.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.243253Z",
     "snapshot_path": "metadata/gongfa/source-software-engineering-truths-81fc7ae.txt",
@@ -12808,7 +12808,7 @@
   "source": {
     "id": "repo-software-engineering-truths-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/software-engineering-truths.md",
+    "path": "docs/gongfa/software-engineering-truths.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.243253Z",
     "snapshot_path": "metadata/gongfa/source-software-engineering-truths-81fc7ae.txt",
@@ -12925,7 +12925,7 @@
   "source": {
     "id": "repo-dataset-first-data-service-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/references/dataset-first-data-service.md",
+    "path": "docs/gongfa/dataset-first-data-service.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.245521Z",
     "snapshot_path": "metadata/gongfa/source-dataset-first-data-service-81fc7ae.txt",
@@ -13037,7 +13037,7 @@
   "source": {
     "id": "repo-development-experience-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/references/development-experience.md",
+    "path": "docs/gongfa/development-experience.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.247888Z",
     "snapshot_path": "metadata/gongfa/source-development-experience-81fc7ae.txt",
@@ -13165,7 +13165,7 @@
   "source": {
     "id": "repo-quality-gates-and-pitfalls-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/references/quality-gates-and-pitfalls.md",
+    "path": "docs/gongfa/quality-gates-and-pitfalls.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.250898Z",
     "snapshot_path": "metadata/gongfa/source-quality-gates-and-pitfalls-81fc7ae.txt",
@@ -28848,7 +28848,7 @@
   "source": {
     "id": "repo-compositional-description-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/compositional-description-model.md",
+    "path": "docs/gongfa/compositional-description-model.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-compositional-description-81fc7ae.txt",
@@ -28973,7 +28973,7 @@
   "source": {
     "id": "repo-thinking-models-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/thinking-models.md",
+    "path": "docs/gongfa/thinking-models.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-thinking-models-81fc7ae.txt",
@@ -29101,7 +29101,7 @@
   "source": {
     "id": "repo-thinking-models-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/thinking-models.md",
+    "path": "docs/gongfa/thinking-models.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-thinking-models-81fc7ae.txt",
@@ -29226,7 +29226,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -29366,7 +29366,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -29508,7 +29508,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -29650,7 +29650,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -29792,7 +29792,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -29933,7 +29933,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -30728,7 +30728,7 @@
   "source": {
     "id": "repo-system-building-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/concepts/system-building.md",
+    "path": "docs/gongfa/system-building.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.363591Z",
     "snapshot_path": "metadata/gongfa/source-system-building-81fc7ae.txt",
@@ -30864,7 +30864,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -30998,7 +30998,7 @@
   "source": {
     "id": "repo-programming-dao-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/programming-dao.md",
+    "path": "docs/gongfa/programming-dao.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.370173Z",
     "snapshot_path": "metadata/gongfa/source-programming-dao-81fc7ae.txt",
@@ -31115,7 +31115,7 @@
   "source": {
     "id": "repo-programming-dao-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/programming-dao.md",
+    "path": "docs/gongfa/programming-dao.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.370173Z",
     "snapshot_path": "metadata/gongfa/source-programming-dao-81fc7ae.txt",
@@ -31237,7 +31237,7 @@
   "source": {
     "id": "repo-software-engineering-truths-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/software-engineering-truths.md",
+    "path": "docs/gongfa/software-engineering-truths.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.243253Z",
     "snapshot_path": "metadata/gongfa/source-software-engineering-truths-81fc7ae.txt",
@@ -31355,7 +31355,7 @@
   "source": {
     "id": "repo-development-experience-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/references/development-experience.md",
+    "path": "docs/gongfa/development-experience.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.247888Z",
     "snapshot_path": "metadata/gongfa/source-development-experience-81fc7ae.txt",
@@ -31465,7 +31465,7 @@
   "source": {
     "id": "repo-development-experience-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/references/development-experience.md",
+    "path": "docs/gongfa/development-experience.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.247888Z",
     "snapshot_path": "metadata/gongfa/source-development-experience-81fc7ae.txt",
@@ -42884,7 +42884,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -43023,7 +43023,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -47195,7 +47195,7 @@
   "source": {
     "id": "repo-thinking-models-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/thinking-models.md",
+    "path": "docs/gongfa/thinking-models.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-thinking-models-81fc7ae.txt",
@@ -47317,7 +47317,7 @@
   "source": {
     "id": "repo-methodology-toolbox-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/philosophy/methodology-toolbox.md",
+    "path": "docs/gongfa/methodology-toolbox.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T04:29:18.396921Z",
     "snapshot_path": "metadata/gongfa/source-methodology-toolbox-81fc7ae.txt",
@@ -47720,7 +47720,7 @@
   "source": {
     "id": "repo-development-experience-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/references/development-experience.md",
+    "path": "docs/gongfa/development-experience.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T09:20:36.247888Z",
     "snapshot_path": "metadata/gongfa/source-development-experience-81fc7ae.txt",
@@ -49295,7 +49295,7 @@
   "source": {
     "id": "repo-recursive-self-optimizing-system-81fc7ae",
     "kind": "repository_document",
-    "path": "docs/concepts/recursive-self-optimizing-system.md",
+    "path": "docs/gongfa/recursive-self-optimizing-system.md",
     "git_revision": "81fc7ae599da7b7b0ce02ea0b069a2c88d288a4e",
     "captured_at": "2026-10-07T06:03:59.367982Z",
     "snapshot_path": "metadata/gongfa/source-recursive-self-optimizing-system-81fc7ae.txt",
